--- a/excel/nickname.xlsx
+++ b/excel/nickname.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12375"/>
+    <workbookView windowWidth="28800" windowHeight="12360"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="105">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="106">
   <si>
     <t>编号</t>
   </si>
@@ -47,6 +47,9 @@
   </si>
   <si>
     <t>nickname</t>
+  </si>
+  <si>
+    <t>int</t>
   </si>
   <si>
     <t>string</t>
@@ -1367,7 +1370,7 @@
         <v>4</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C3" s="4"/>
     </row>
@@ -1376,7 +1379,7 @@
         <v>0</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -1384,7 +1387,7 @@
         <v>1</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="6" spans="1:3">
@@ -1392,7 +1395,7 @@
         <v>2</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="7" spans="1:3">
@@ -1400,7 +1403,7 @@
         <v>3</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -1408,7 +1411,7 @@
         <v>4</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="9" spans="1:3">
@@ -1416,7 +1419,7 @@
         <v>5</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="10" spans="1:3">
@@ -1424,7 +1427,7 @@
         <v>6</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="11" spans="1:3">
@@ -1432,7 +1435,7 @@
         <v>7</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="12" spans="1:3">
@@ -1440,7 +1443,7 @@
         <v>8</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="13" spans="1:3">
@@ -1448,7 +1451,7 @@
         <v>9</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="14" spans="1:3">
@@ -1456,7 +1459,7 @@
         <v>10</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="15" spans="1:3">
@@ -1464,7 +1467,7 @@
         <v>11</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="16" spans="1:3">
@@ -1472,7 +1475,7 @@
         <v>12</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -1480,7 +1483,7 @@
         <v>13</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -1488,7 +1491,7 @@
         <v>14</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -1496,7 +1499,7 @@
         <v>15</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -1504,7 +1507,7 @@
         <v>16</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -1512,7 +1515,7 @@
         <v>17</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="22" spans="1:2">
@@ -1520,7 +1523,7 @@
         <v>18</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -1528,7 +1531,7 @@
         <v>19</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -1536,7 +1539,7 @@
         <v>20</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -1544,7 +1547,7 @@
         <v>21</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="26" spans="1:2">
@@ -1552,7 +1555,7 @@
         <v>22</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="27" spans="1:2">
@@ -1560,7 +1563,7 @@
         <v>23</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="28" spans="1:2">
@@ -1568,7 +1571,7 @@
         <v>24</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="29" spans="1:2">
@@ -1576,7 +1579,7 @@
         <v>25</v>
       </c>
       <c r="B29" s="4" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="30" spans="1:2">
@@ -1584,7 +1587,7 @@
         <v>26</v>
       </c>
       <c r="B30" s="4" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="31" spans="1:2">
@@ -1592,7 +1595,7 @@
         <v>27</v>
       </c>
       <c r="B31" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="32" spans="1:2">
@@ -1600,7 +1603,7 @@
         <v>28</v>
       </c>
       <c r="B32" s="4" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="33" spans="1:2">
@@ -1608,7 +1611,7 @@
         <v>29</v>
       </c>
       <c r="B33" s="4" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="34" spans="1:2">
@@ -1616,7 +1619,7 @@
         <v>30</v>
       </c>
       <c r="B34" s="4" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="35" spans="1:2">
@@ -1624,7 +1627,7 @@
         <v>31</v>
       </c>
       <c r="B35" s="4" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="36" spans="1:2">
@@ -1632,7 +1635,7 @@
         <v>32</v>
       </c>
       <c r="B36" s="4" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="37" spans="1:2">
@@ -1640,7 +1643,7 @@
         <v>33</v>
       </c>
       <c r="B37" s="4" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="38" spans="1:2">
@@ -1648,7 +1651,7 @@
         <v>34</v>
       </c>
       <c r="B38" s="4" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="39" spans="1:2">
@@ -1656,7 +1659,7 @@
         <v>35</v>
       </c>
       <c r="B39" s="4" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="40" spans="1:2">
@@ -1664,7 +1667,7 @@
         <v>36</v>
       </c>
       <c r="B40" s="4" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="41" spans="1:2">
@@ -1672,7 +1675,7 @@
         <v>37</v>
       </c>
       <c r="B41" s="4" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="42" spans="1:2">
@@ -1680,7 +1683,7 @@
         <v>38</v>
       </c>
       <c r="B42" s="4" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -1688,7 +1691,7 @@
         <v>39</v>
       </c>
       <c r="B43" s="4" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -1696,7 +1699,7 @@
         <v>40</v>
       </c>
       <c r="B44" s="4" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -1704,7 +1707,7 @@
         <v>41</v>
       </c>
       <c r="B45" s="4" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -1712,7 +1715,7 @@
         <v>42</v>
       </c>
       <c r="B46" s="4" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -1720,7 +1723,7 @@
         <v>43</v>
       </c>
       <c r="B47" s="4" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -1728,7 +1731,7 @@
         <v>44</v>
       </c>
       <c r="B48" s="4" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -1736,7 +1739,7 @@
         <v>45</v>
       </c>
       <c r="B49" s="4" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -1744,7 +1747,7 @@
         <v>46</v>
       </c>
       <c r="B50" s="4" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -1752,7 +1755,7 @@
         <v>47</v>
       </c>
       <c r="B51" s="4" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -1760,7 +1763,7 @@
         <v>48</v>
       </c>
       <c r="B52" s="4" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -1768,7 +1771,7 @@
         <v>49</v>
       </c>
       <c r="B53" s="4" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -1776,7 +1779,7 @@
         <v>50</v>
       </c>
       <c r="B54" s="4" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -1784,7 +1787,7 @@
         <v>51</v>
       </c>
       <c r="B55" s="4" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -1792,7 +1795,7 @@
         <v>52</v>
       </c>
       <c r="B56" s="4" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -1800,7 +1803,7 @@
         <v>53</v>
       </c>
       <c r="B57" s="4" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -1808,7 +1811,7 @@
         <v>54</v>
       </c>
       <c r="B58" s="4" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -1816,7 +1819,7 @@
         <v>55</v>
       </c>
       <c r="B59" s="4" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -1824,7 +1827,7 @@
         <v>56</v>
       </c>
       <c r="B60" s="4" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -1832,7 +1835,7 @@
         <v>57</v>
       </c>
       <c r="B61" s="4" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -1840,7 +1843,7 @@
         <v>58</v>
       </c>
       <c r="B62" s="4" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -1848,7 +1851,7 @@
         <v>59</v>
       </c>
       <c r="B63" s="4" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -1856,7 +1859,7 @@
         <v>60</v>
       </c>
       <c r="B64" s="4" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -1864,7 +1867,7 @@
         <v>61</v>
       </c>
       <c r="B65" s="4" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -1872,7 +1875,7 @@
         <v>62</v>
       </c>
       <c r="B66" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -1880,7 +1883,7 @@
         <v>63</v>
       </c>
       <c r="B67" s="4" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -1888,7 +1891,7 @@
         <v>64</v>
       </c>
       <c r="B68" s="4" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -1896,7 +1899,7 @@
         <v>65</v>
       </c>
       <c r="B69" s="4" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -1904,7 +1907,7 @@
         <v>66</v>
       </c>
       <c r="B70" s="4" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -1912,7 +1915,7 @@
         <v>67</v>
       </c>
       <c r="B71" s="4" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -1920,7 +1923,7 @@
         <v>68</v>
       </c>
       <c r="B72" s="4" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -1928,7 +1931,7 @@
         <v>69</v>
       </c>
       <c r="B73" s="4" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -1936,7 +1939,7 @@
         <v>70</v>
       </c>
       <c r="B74" s="4" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -1944,7 +1947,7 @@
         <v>71</v>
       </c>
       <c r="B75" s="4" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -1952,7 +1955,7 @@
         <v>72</v>
       </c>
       <c r="B76" s="4" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1960,7 +1963,7 @@
         <v>73</v>
       </c>
       <c r="B77" s="4" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1968,7 +1971,7 @@
         <v>74</v>
       </c>
       <c r="B78" s="4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1976,7 +1979,7 @@
         <v>75</v>
       </c>
       <c r="B79" s="4" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1984,7 +1987,7 @@
         <v>76</v>
       </c>
       <c r="B80" s="4" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1992,7 +1995,7 @@
         <v>77</v>
       </c>
       <c r="B81" s="4" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -2000,7 +2003,7 @@
         <v>78</v>
       </c>
       <c r="B82" s="4" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -2008,7 +2011,7 @@
         <v>79</v>
       </c>
       <c r="B83" s="4" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -2016,7 +2019,7 @@
         <v>80</v>
       </c>
       <c r="B84" s="4" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -2024,7 +2027,7 @@
         <v>81</v>
       </c>
       <c r="B85" s="4" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -2032,7 +2035,7 @@
         <v>82</v>
       </c>
       <c r="B86" s="4" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -2040,7 +2043,7 @@
         <v>83</v>
       </c>
       <c r="B87" s="4" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -2048,7 +2051,7 @@
         <v>84</v>
       </c>
       <c r="B88" s="4" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -2056,7 +2059,7 @@
         <v>85</v>
       </c>
       <c r="B89" s="4" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -2064,7 +2067,7 @@
         <v>86</v>
       </c>
       <c r="B90" s="4" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -2072,7 +2075,7 @@
         <v>87</v>
       </c>
       <c r="B91" s="4" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -2080,7 +2083,7 @@
         <v>88</v>
       </c>
       <c r="B92" s="4" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -2088,7 +2091,7 @@
         <v>89</v>
       </c>
       <c r="B93" s="4" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -2096,7 +2099,7 @@
         <v>90</v>
       </c>
       <c r="B94" s="4" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -2104,7 +2107,7 @@
         <v>91</v>
       </c>
       <c r="B95" s="4" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -2112,7 +2115,7 @@
         <v>92</v>
       </c>
       <c r="B96" s="4" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
     </row>
     <row r="97" spans="1:3">
@@ -2120,7 +2123,7 @@
         <v>93</v>
       </c>
       <c r="B97" s="4" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="98" spans="1:3">
@@ -2128,7 +2131,7 @@
         <v>94</v>
       </c>
       <c r="B98" s="4" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="99" spans="1:3">
@@ -2136,7 +2139,7 @@
         <v>95</v>
       </c>
       <c r="B99" s="4" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="100" spans="1:3">
@@ -2144,7 +2147,7 @@
         <v>96</v>
       </c>
       <c r="B100" s="4" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C100" s="6"/>
     </row>
@@ -2153,7 +2156,7 @@
         <v>97</v>
       </c>
       <c r="B101" s="4" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
     </row>
     <row r="102" spans="1:3">
@@ -2161,7 +2164,7 @@
         <v>98</v>
       </c>
       <c r="B102" s="4" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
     </row>
     <row r="103" spans="1:3">
@@ -2169,7 +2172,7 @@
         <v>99</v>
       </c>
       <c r="B103" s="4" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
     </row>
     <row r="104" spans="1:3">
